--- a/Bases_de_Dados/FootyStats/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP114"/>
+  <dimension ref="A1:BP115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.09</v>
@@ -4184,7 +4184,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR17" t="n">
         <v>2.16</v>
@@ -5271,7 +5271,7 @@
         <v>1</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.8</v>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.33</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ33" t="n">
         <v>1.22</v>
@@ -8108,7 +8108,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR35" t="n">
         <v>1.25</v>
@@ -9634,7 +9634,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR42" t="n">
         <v>1</v>
@@ -10724,7 +10724,7 @@
         <v>1</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR47" t="n">
         <v>1.38</v>
@@ -10939,7 +10939,7 @@
         <v>1</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ48" t="n">
         <v>2.2</v>
@@ -11596,7 +11596,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR51" t="n">
         <v>1.78</v>
@@ -12247,7 +12247,7 @@
         <v>1</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ54" t="n">
         <v>1.25</v>
@@ -14648,7 +14648,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR65" t="n">
         <v>1.63</v>
@@ -15956,7 +15956,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR71" t="n">
         <v>1.24</v>
@@ -16389,7 +16389,7 @@
         <v>0.6</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.22</v>
@@ -19226,7 +19226,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR86" t="n">
         <v>1.91</v>
@@ -19441,7 +19441,7 @@
         <v>1.29</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ87" t="n">
         <v>1.1</v>
@@ -20749,7 +20749,7 @@
         <v>0.88</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.3</v>
@@ -21188,7 +21188,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR95" t="n">
         <v>2.12</v>
@@ -23365,7 +23365,7 @@
         <v>1.67</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ105" t="n">
         <v>1.8</v>
@@ -25406,6 +25406,224 @@
       </c>
       <c r="BP114" t="n">
         <v>1.58</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="n">
+        <v>8266566</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>46081.95833333334</v>
+      </c>
+      <c r="F115" t="n">
+        <v>19</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Wellington Phoenix</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sydney FC</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1</v>
+      </c>
+      <c r="N115" t="n">
+        <v>1</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>['49']</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R115" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S115" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T115" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U115" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V115" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="W115" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X115" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AK115" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM115" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ115" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR115" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS115" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AT115" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU115" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV115" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW115" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX115" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY115" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ115" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA115" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB115" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC115" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD115" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BE115" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="BF115" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BG115" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH115" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI115" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ115" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BK115" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL115" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BM115" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BN115" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO115" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP115" t="n">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Australia A-League_20252026.xlsx
@@ -24915,13 +24915,13 @@
         <v>7</v>
       </c>
       <c r="AX112" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY112" t="n">
         <v>13</v>
       </c>
       <c r="AZ112" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA112" t="n">
         <v>5</v>
@@ -25130,13 +25130,13 @@
         <v>0</v>
       </c>
       <c r="AW113" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX113" t="n">
         <v>9</v>
       </c>
       <c r="AY113" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ113" t="n">
         <v>9</v>

--- a/Bases_de_Dados/FootyStats/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP115"/>
+  <dimension ref="A1:BP116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2876,7 +2876,7 @@
         <v>2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.22</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ18" t="n">
         <v>0.78</v>
@@ -5056,7 +5056,7 @@
         <v>1</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR21" t="n">
         <v>1.35</v>
@@ -6582,7 +6582,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR28" t="n">
         <v>1.23</v>
@@ -8541,7 +8541,7 @@
         <v>1.5</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ37" t="n">
         <v>1.22</v>
@@ -8759,7 +8759,7 @@
         <v>0.75</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.3</v>
@@ -11157,7 +11157,7 @@
         <v>1.25</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.09</v>
@@ -12250,7 +12250,7 @@
         <v>1</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR54" t="n">
         <v>1.75</v>
@@ -14866,7 +14866,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR66" t="n">
         <v>1.38</v>
@@ -15081,7 +15081,7 @@
         <v>2.5</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ67" t="n">
         <v>1.8</v>
@@ -15953,7 +15953,7 @@
         <v>1.43</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ71" t="n">
         <v>1.45</v>
@@ -16174,7 +16174,7 @@
         <v>1</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR72" t="n">
         <v>1.44</v>
@@ -18354,7 +18354,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR82" t="n">
         <v>2.07</v>
@@ -18787,7 +18787,7 @@
         <v>1.5</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ84" t="n">
         <v>1.1</v>
@@ -20967,7 +20967,7 @@
         <v>1.5</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ94" t="n">
         <v>1.22</v>
@@ -21406,7 +21406,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR96" t="n">
         <v>1.5</v>
@@ -25327,7 +25327,7 @@
         <v>0.5</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ114" t="n">
         <v>0.78</v>
@@ -25624,6 +25624,224 @@
       </c>
       <c r="BP115" t="n">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="n">
+        <v>8266553</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>46085.20833333334</v>
+      </c>
+      <c r="F116" t="n">
+        <v>20</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Macarthur</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Central Coast Mariners</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>1</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1</v>
+      </c>
+      <c r="L116" t="n">
+        <v>1</v>
+      </c>
+      <c r="M116" t="n">
+        <v>3</v>
+      </c>
+      <c r="N116" t="n">
+        <v>4</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>['67']</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>['37', '65', '84']</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R116" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S116" t="n">
+        <v>5</v>
+      </c>
+      <c r="T116" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="U116" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="V116" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W116" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X116" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK116" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM116" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP116" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ116" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR116" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS116" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AT116" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AU116" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV116" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW116" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX116" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY116" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ116" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA116" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB116" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC116" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD116" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BE116" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF116" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BG116" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH116" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI116" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ116" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK116" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL116" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BM116" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BN116" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BO116" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BP116" t="n">
+        <v>1.51</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP116"/>
+  <dimension ref="A1:BP117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.45</v>
@@ -1786,7 +1786,7 @@
         <v>1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR19" t="n">
         <v>1.44</v>
@@ -4835,7 +4835,7 @@
         <v>0.5</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ20" t="n">
         <v>0.78</v>
@@ -6143,7 +6143,7 @@
         <v>1.67</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ26" t="n">
         <v>1.1</v>
@@ -9198,7 +9198,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR40" t="n">
         <v>1.85</v>
@@ -9849,7 +9849,7 @@
         <v>0.5</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.09</v>
@@ -12901,7 +12901,7 @@
         <v>0.25</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ57" t="n">
         <v>0.78</v>
@@ -13340,7 +13340,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR59" t="n">
         <v>1.93</v>
@@ -14430,7 +14430,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR64" t="n">
         <v>1.15</v>
@@ -14863,7 +14863,7 @@
         <v>0.75</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ66" t="n">
         <v>1.44</v>
@@ -17697,7 +17697,7 @@
         <v>1.17</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.3</v>
@@ -17918,7 +17918,7 @@
         <v>2</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR80" t="n">
         <v>1.99</v>
@@ -18136,7 +18136,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR81" t="n">
         <v>2.02</v>
@@ -19659,7 +19659,7 @@
         <v>1.57</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ88" t="n">
         <v>1.33</v>
@@ -21839,7 +21839,7 @@
         <v>2.14</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ98" t="n">
         <v>2.2</v>
@@ -22060,7 +22060,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR99" t="n">
         <v>1.56</v>
@@ -23147,7 +23147,7 @@
         <v>1.43</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ104" t="n">
         <v>1.22</v>
@@ -25781,19 +25781,19 @@
         <v>5</v>
       </c>
       <c r="AV116" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW116" t="n">
         <v>7</v>
-      </c>
-      <c r="AW116" t="n">
-        <v>6</v>
       </c>
       <c r="AX116" t="n">
         <v>4</v>
       </c>
       <c r="AY116" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ116" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA116" t="n">
         <v>3</v>
@@ -25842,6 +25842,224 @@
       </c>
       <c r="BP116" t="n">
         <v>1.51</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="n">
+        <v>8266561</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>46087.23263888889</v>
+      </c>
+      <c r="F117" t="n">
+        <v>20</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Adelaide United</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Wellington Phoenix</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>1</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1</v>
+      </c>
+      <c r="L117" t="n">
+        <v>1</v>
+      </c>
+      <c r="M117" t="n">
+        <v>1</v>
+      </c>
+      <c r="N117" t="n">
+        <v>2</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>['35']</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R117" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="S117" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="T117" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="U117" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V117" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W117" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X117" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP117"/>
+  <dimension ref="A1:BP119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.44</v>
@@ -3748,7 +3748,7 @@
         <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR15" t="n">
         <v>1.27</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.45</v>
@@ -4402,7 +4402,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR18" t="n">
         <v>1.75</v>
@@ -4838,7 +4838,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR20" t="n">
         <v>1.51</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AQ24" t="n">
         <v>1.33</v>
@@ -6797,10 +6797,10 @@
         <v>1.5</v>
       </c>
       <c r="AP29" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR29" t="n">
         <v>2.16</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ31" t="n">
         <v>1.22</v>
@@ -7454,7 +7454,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR32" t="n">
         <v>1.15</v>
@@ -8762,7 +8762,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR38" t="n">
         <v>1.37</v>
@@ -8980,7 +8980,7 @@
         <v>1</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR39" t="n">
         <v>1.46</v>
@@ -9413,7 +9413,7 @@
         <v>1.2</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.1</v>
@@ -11593,7 +11593,7 @@
         <v>1.8</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.45</v>
@@ -11814,7 +11814,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR52" t="n">
         <v>1.6</v>
@@ -12683,7 +12683,7 @@
         <v>1</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.33</v>
@@ -12904,7 +12904,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR57" t="n">
         <v>1.44</v>
@@ -15738,7 +15738,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ70" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR70" t="n">
         <v>1.97</v>
@@ -17700,7 +17700,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR79" t="n">
         <v>1.53</v>
@@ -17915,7 +17915,7 @@
         <v>1</v>
       </c>
       <c r="AP80" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.11</v>
@@ -18133,7 +18133,7 @@
         <v>1.33</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ81" t="n">
         <v>1.11</v>
@@ -19877,7 +19877,7 @@
         <v>1.38</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.09</v>
@@ -20095,10 +20095,10 @@
         <v>0.67</v>
       </c>
       <c r="AP90" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR90" t="n">
         <v>1.85</v>
@@ -20534,7 +20534,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR92" t="n">
         <v>1.02</v>
@@ -20752,7 +20752,7 @@
         <v>1</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR93" t="n">
         <v>1.63</v>
@@ -22711,7 +22711,7 @@
         <v>1</v>
       </c>
       <c r="AP102" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AQ102" t="n">
         <v>1.22</v>
@@ -22929,7 +22929,7 @@
         <v>1.75</v>
       </c>
       <c r="AP103" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AQ103" t="n">
         <v>1.8</v>
@@ -23583,7 +23583,7 @@
         <v>1.2</v>
       </c>
       <c r="AP106" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AQ106" t="n">
         <v>1.09</v>
@@ -23804,7 +23804,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR107" t="n">
         <v>1.66</v>
@@ -24022,7 +24022,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ108" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR108" t="n">
         <v>0.98</v>
@@ -24237,7 +24237,7 @@
         <v>1.5</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ109" t="n">
         <v>1.33</v>
@@ -25330,7 +25330,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ114" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR114" t="n">
         <v>1.41</v>
@@ -25999,7 +25999,7 @@
         <v>5</v>
       </c>
       <c r="AV117" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW117" t="n">
         <v>14</v>
@@ -26011,16 +26011,16 @@
         <v>19</v>
       </c>
       <c r="AZ117" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA117" t="n">
         <v>9</v>
       </c>
       <c r="BB117" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC117" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD117" t="n">
         <v>1.44</v>
@@ -26060,6 +26060,442 @@
       </c>
       <c r="BP117" t="n">
         <v>1.54</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="n">
+        <v>8266557</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>46088.125</v>
+      </c>
+      <c r="F118" t="n">
+        <v>20</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Newcastle Jets FC</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Western Sydney Wanderers</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>1</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1</v>
+      </c>
+      <c r="L118" t="n">
+        <v>2</v>
+      </c>
+      <c r="M118" t="n">
+        <v>1</v>
+      </c>
+      <c r="N118" t="n">
+        <v>3</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>['47', '77']</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>['20']</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R118" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S118" t="n">
+        <v>3</v>
+      </c>
+      <c r="T118" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="U118" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="V118" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="W118" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="X118" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="n">
+        <v>8266567</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>46088.23263888889</v>
+      </c>
+      <c r="F119" t="n">
+        <v>20</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Sydney FC</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Melbourne Victory FC</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>1</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1</v>
+      </c>
+      <c r="L119" t="n">
+        <v>2</v>
+      </c>
+      <c r="M119" t="n">
+        <v>2</v>
+      </c>
+      <c r="N119" t="n">
+        <v>4</v>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>['73', '75']</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>['34', '69']</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="R119" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="S119" t="n">
+        <v>3</v>
+      </c>
+      <c r="T119" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U119" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V119" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W119" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X119" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP119"/>
+  <dimension ref="A1:BP120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ9" t="n">
         <v>0.7</v>
@@ -2658,7 +2658,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.22</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.09</v>
@@ -7236,7 +7236,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR31" t="n">
         <v>1.8</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ36" t="n">
         <v>2.2</v>
@@ -8544,7 +8544,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR37" t="n">
         <v>1.49</v>
@@ -9195,7 +9195,7 @@
         <v>1</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.11</v>
@@ -13122,7 +13122,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR58" t="n">
         <v>1.56</v>
@@ -13773,7 +13773,7 @@
         <v>1.5</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ61" t="n">
         <v>2.2</v>
@@ -14212,7 +14212,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR63" t="n">
         <v>1.93</v>
@@ -18351,7 +18351,7 @@
         <v>1</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.44</v>
@@ -19008,7 +19008,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR85" t="n">
         <v>1.47</v>
@@ -20970,7 +20970,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR94" t="n">
         <v>1.33</v>
@@ -21185,7 +21185,7 @@
         <v>1.44</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.45</v>
@@ -23150,7 +23150,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR104" t="n">
         <v>1.6</v>
@@ -24673,7 +24673,7 @@
         <v>1.22</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.1</v>
@@ -25112,7 +25112,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR113" t="n">
         <v>1.46</v>
@@ -26496,6 +26496,224 @@
       </c>
       <c r="BP119" t="n">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="n">
+        <v>8266569</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>46088.95833333334</v>
+      </c>
+      <c r="F120" t="n">
+        <v>20</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Perth Glory FC</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>1</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1</v>
+      </c>
+      <c r="K120" t="n">
+        <v>2</v>
+      </c>
+      <c r="L120" t="n">
+        <v>2</v>
+      </c>
+      <c r="M120" t="n">
+        <v>2</v>
+      </c>
+      <c r="N120" t="n">
+        <v>4</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>['7', '61']</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>['39', '57']</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R120" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S120" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="T120" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U120" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V120" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W120" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X120" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>
